--- a/public/files/price-list.xlsx
+++ b/public/files/price-list.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прайс-лист" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Прайс-лист" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -490,6 +490,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -682,7 +683,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Кета (икола)</t>
+          <t>Кета (юкола)</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">

--- a/public/files/price-list.xlsx
+++ b/public/files/price-list.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -948,6 +947,19 @@
       </c>
       <c r="C40" s="6" t="n">
         <v>400</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>35</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Камбала икряная х/к</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1100</v>
       </c>
     </row>
   </sheetData>
